--- a/template/合宿前資料_テンプレ.xlsx
+++ b/template/合宿前資料_テンプレ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30321"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30403"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0bca17f66a05bfa2/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0bca17f66a05bfa2/ドキュメント/GitHub/huac_flight/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{818B95BF-608D-4203-8F28-F4865FC1EBFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E53FFB89-D0E3-4E50-B074-2A2E6F2194C7}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +205,15 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -595,7 +604,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -638,49 +647,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1026,95 +1038,100 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="19" width="11.5" style="1" customWidth="1"/>
+    <col min="2" max="10" width="11.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="29" customWidth="1"/>
+    <col min="12" max="15" width="11.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="29" customWidth="1"/>
+    <col min="17" max="18" width="11.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="29" customWidth="1"/>
     <col min="20" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="18" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="18" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="21" t="s">
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="19"/>
-      <c r="S1" s="20"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="22"/>
     </row>
     <row r="2" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="Q2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="R2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="26" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1129,15 +1146,15 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="15"/>
+      <c r="K3" s="27"/>
       <c r="L3" s="8"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="15"/>
+      <c r="P3" s="27"/>
       <c r="Q3" s="12"/>
       <c r="R3" s="11"/>
-      <c r="S3" s="15"/>
+      <c r="S3" s="27"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
@@ -1150,15 +1167,15 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="16"/>
+      <c r="K4" s="28"/>
       <c r="L4" s="4"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="16"/>
+      <c r="P4" s="28"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="16"/>
+      <c r="S4" s="28"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
@@ -1171,15 +1188,15 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="16"/>
+      <c r="K5" s="28"/>
       <c r="L5" s="4"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="16"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="16"/>
+      <c r="S5" s="28"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
@@ -1192,15 +1209,15 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="16"/>
+      <c r="K6" s="28"/>
       <c r="L6" s="4"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="16"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="3"/>
-      <c r="S6" s="16"/>
+      <c r="S6" s="28"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
@@ -1213,15 +1230,15 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="16"/>
+      <c r="K7" s="28"/>
       <c r="L7" s="4"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="16"/>
+      <c r="P7" s="28"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="28"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
@@ -1234,15 +1251,15 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="16"/>
+      <c r="K8" s="28"/>
       <c r="L8" s="4"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="16"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="13"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="16"/>
+      <c r="S8" s="28"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
@@ -1255,15 +1272,15 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="16"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="4"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="16"/>
+      <c r="P9" s="28"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="16"/>
+      <c r="S9" s="28"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
@@ -1276,15 +1293,15 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="16"/>
+      <c r="K10" s="28"/>
       <c r="L10" s="4"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="16"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="28"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
@@ -1297,15 +1314,15 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="16"/>
+      <c r="K11" s="28"/>
       <c r="L11" s="4"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="16"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="16"/>
+      <c r="S11" s="28"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
@@ -1318,15 +1335,15 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="16"/>
+      <c r="K12" s="28"/>
       <c r="L12" s="4"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="16"/>
+      <c r="P12" s="28"/>
       <c r="Q12" s="13"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="16"/>
+      <c r="S12" s="28"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
@@ -1339,15 +1356,15 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="16"/>
+      <c r="K13" s="28"/>
       <c r="L13" s="4"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="16"/>
+      <c r="P13" s="28"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="28"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
@@ -1360,15 +1377,15 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="16"/>
+      <c r="K14" s="28"/>
       <c r="L14" s="4"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="16"/>
+      <c r="P14" s="28"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="16"/>
+      <c r="S14" s="28"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="6"/>
@@ -1381,15 +1398,15 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="16"/>
+      <c r="K15" s="28"/>
       <c r="L15" s="4"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="16"/>
+      <c r="P15" s="28"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="16"/>
+      <c r="S15" s="28"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
@@ -1402,15 +1419,15 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="16"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="4"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="16"/>
+      <c r="P16" s="28"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="16"/>
+      <c r="S16" s="28"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
@@ -1423,15 +1440,15 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="16"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="4"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="16"/>
+      <c r="P17" s="28"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="16"/>
+      <c r="S17" s="28"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
@@ -1444,15 +1461,15 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="16"/>
+      <c r="K18" s="28"/>
       <c r="L18" s="4"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="16"/>
+      <c r="P18" s="28"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="16"/>
+      <c r="S18" s="28"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
@@ -1465,15 +1482,15 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="16"/>
+      <c r="K19" s="28"/>
       <c r="L19" s="4"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="16"/>
+      <c r="P19" s="28"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="16"/>
+      <c r="S19" s="28"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
@@ -1486,15 +1503,15 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="16"/>
+      <c r="K20" s="28"/>
       <c r="L20" s="4"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="16"/>
+      <c r="P20" s="28"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="16"/>
+      <c r="S20" s="28"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
@@ -1507,15 +1524,15 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="16"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="16"/>
+      <c r="P21" s="28"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="3"/>
-      <c r="S21" s="16"/>
+      <c r="S21" s="28"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
@@ -1528,15 +1545,15 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="16"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="4"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="16"/>
+      <c r="P22" s="28"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="3"/>
-      <c r="S22" s="16"/>
+      <c r="S22" s="28"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
@@ -1549,15 +1566,15 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="16"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="16"/>
+      <c r="P23" s="28"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="3"/>
-      <c r="S23" s="16"/>
+      <c r="S23" s="28"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
@@ -1570,15 +1587,15 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="16"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="16"/>
+      <c r="P24" s="28"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="16"/>
+      <c r="S24" s="28"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="6"/>
@@ -1591,15 +1608,15 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="16"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="16"/>
+      <c r="P25" s="28"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="16"/>
+      <c r="S25" s="28"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
@@ -1612,15 +1629,15 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="16"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="16"/>
+      <c r="P26" s="28"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="16"/>
+      <c r="S26" s="28"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
@@ -1633,15 +1650,15 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="16"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="16"/>
+      <c r="P27" s="28"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="16"/>
+      <c r="S27" s="28"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
@@ -1654,15 +1671,15 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="16"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="16"/>
+      <c r="P28" s="28"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="3"/>
-      <c r="S28" s="16"/>
+      <c r="S28" s="28"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="6"/>
@@ -1675,15 +1692,15 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="16"/>
+      <c r="K29" s="28"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="16"/>
+      <c r="P29" s="28"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="3"/>
-      <c r="S29" s="16"/>
+      <c r="S29" s="28"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
@@ -1696,15 +1713,15 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="16"/>
+      <c r="K30" s="28"/>
       <c r="L30" s="4"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="16"/>
+      <c r="P30" s="28"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="3"/>
-      <c r="S30" s="16"/>
+      <c r="S30" s="28"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
@@ -1717,15 +1734,15 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="16"/>
+      <c r="K31" s="28"/>
       <c r="L31" s="4"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="16"/>
+      <c r="P31" s="28"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="16"/>
+      <c r="S31" s="28"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="6"/>
@@ -1738,15 +1755,15 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="16"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="4"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="3"/>
-      <c r="P32" s="16"/>
+      <c r="P32" s="28"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="3"/>
-      <c r="S32" s="16"/>
+      <c r="S32" s="28"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="6"/>
@@ -1759,15 +1776,15 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="16"/>
+      <c r="K33" s="28"/>
       <c r="L33" s="4"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="16"/>
+      <c r="P33" s="28"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="16"/>
+      <c r="S33" s="28"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="6"/>
@@ -1780,15 +1797,15 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="16"/>
+      <c r="K34" s="28"/>
       <c r="L34" s="4"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="16"/>
+      <c r="P34" s="28"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="3"/>
-      <c r="S34" s="16"/>
+      <c r="S34" s="28"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="6"/>
@@ -1801,15 +1818,15 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="16"/>
+      <c r="K35" s="28"/>
       <c r="L35" s="4"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="3"/>
-      <c r="P35" s="16"/>
+      <c r="P35" s="28"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="3"/>
-      <c r="S35" s="16"/>
+      <c r="S35" s="28"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="6"/>
@@ -1822,15 +1839,15 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="16"/>
+      <c r="K36" s="28"/>
       <c r="L36" s="4"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="16"/>
+      <c r="P36" s="28"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="3"/>
-      <c r="S36" s="16"/>
+      <c r="S36" s="28"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="6"/>
@@ -1843,15 +1860,15 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="16"/>
+      <c r="K37" s="28"/>
       <c r="L37" s="4"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="16"/>
+      <c r="P37" s="28"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="3"/>
-      <c r="S37" s="16"/>
+      <c r="S37" s="28"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="6"/>
@@ -1864,15 +1881,15 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="16"/>
+      <c r="K38" s="28"/>
       <c r="L38" s="4"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="16"/>
+      <c r="P38" s="28"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="3"/>
-      <c r="S38" s="16"/>
+      <c r="S38" s="28"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="6"/>
@@ -1885,15 +1902,15 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="16"/>
+      <c r="K39" s="28"/>
       <c r="L39" s="4"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="16"/>
+      <c r="P39" s="28"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="16"/>
+      <c r="S39" s="28"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="6"/>
@@ -1906,15 +1923,15 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="16"/>
+      <c r="K40" s="28"/>
       <c r="L40" s="4"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="16"/>
+      <c r="P40" s="28"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="16"/>
+      <c r="S40" s="28"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="6"/>
@@ -1927,15 +1944,15 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="16"/>
+      <c r="K41" s="28"/>
       <c r="L41" s="4"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="16"/>
+      <c r="P41" s="28"/>
       <c r="Q41" s="13"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="16"/>
+      <c r="S41" s="28"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="6"/>
@@ -1948,15 +1965,15 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="16"/>
+      <c r="K42" s="28"/>
       <c r="L42" s="4"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="16"/>
+      <c r="P42" s="28"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="3"/>
-      <c r="S42" s="16"/>
+      <c r="S42" s="28"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A43" s="6"/>
@@ -1969,15 +1986,15 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="16"/>
+      <c r="K43" s="28"/>
       <c r="L43" s="4"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="16"/>
+      <c r="P43" s="28"/>
       <c r="Q43" s="13"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="16"/>
+      <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="6"/>
@@ -1990,15 +2007,15 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="16"/>
+      <c r="K44" s="28"/>
       <c r="L44" s="4"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="16"/>
+      <c r="P44" s="28"/>
       <c r="Q44" s="13"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="16"/>
+      <c r="S44" s="28"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="6"/>
@@ -2011,15 +2028,15 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="16"/>
+      <c r="K45" s="28"/>
       <c r="L45" s="4"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="16"/>
+      <c r="P45" s="28"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="16"/>
+      <c r="S45" s="28"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="6"/>
@@ -2032,15 +2049,15 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="16"/>
+      <c r="K46" s="28"/>
       <c r="L46" s="4"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="16"/>
+      <c r="P46" s="28"/>
       <c r="Q46" s="13"/>
       <c r="R46" s="3"/>
-      <c r="S46" s="16"/>
+      <c r="S46" s="28"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="6"/>
@@ -2053,15 +2070,15 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="16"/>
+      <c r="K47" s="28"/>
       <c r="L47" s="4"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="16"/>
+      <c r="P47" s="28"/>
       <c r="Q47" s="13"/>
       <c r="R47" s="3"/>
-      <c r="S47" s="16"/>
+      <c r="S47" s="28"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="6"/>
@@ -2074,15 +2091,15 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="16"/>
+      <c r="K48" s="28"/>
       <c r="L48" s="4"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="16"/>
+      <c r="P48" s="28"/>
       <c r="Q48" s="13"/>
       <c r="R48" s="3"/>
-      <c r="S48" s="16"/>
+      <c r="S48" s="28"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="6"/>
@@ -2095,15 +2112,15 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="16"/>
+      <c r="K49" s="28"/>
       <c r="L49" s="4"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="16"/>
+      <c r="P49" s="28"/>
       <c r="Q49" s="13"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="16"/>
+      <c r="S49" s="28"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="6"/>
@@ -2116,15 +2133,15 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="16"/>
+      <c r="K50" s="28"/>
       <c r="L50" s="4"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="16"/>
+      <c r="P50" s="28"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="3"/>
-      <c r="S50" s="16"/>
+      <c r="S50" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/template/合宿前資料_テンプレ.xlsx
+++ b/template/合宿前資料_テンプレ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0bca17f66a05bfa2/ドキュメント/GitHub/huac_flight/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{818B95BF-608D-4203-8F28-F4865FC1EBFE}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7A953E-942D-4A9F-8882-C28625805A67}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E53FFB89-D0E3-4E50-B074-2A2E6F2194C7}"/>
   </bookViews>
@@ -238,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -513,7 +513,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -521,6 +521,36 @@
     <border>
       <left/>
       <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -530,67 +560,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="dotted">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -604,7 +580,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -641,12 +617,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -662,7 +638,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,25 +659,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1039,47 +1009,47 @@
   <cols>
     <col min="1" max="1" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="11.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="29" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="22" customWidth="1"/>
     <col min="12" max="15" width="11.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5" style="29" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="22" customWidth="1"/>
     <col min="17" max="18" width="11.5" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5" style="29" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="22" customWidth="1"/>
     <col min="20" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="20" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="22"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="25"/>
       <c r="Q1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="21"/>
-      <c r="S1" s="22"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="25"/>
     </row>
     <row r="2" spans="1:19" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="25"/>
+      <c r="A2" s="27"/>
       <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
@@ -1107,7 +1077,7 @@
       <c r="J2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="19" t="s">
         <v>18</v>
       </c>
       <c r="L2" s="14" t="s">
@@ -1122,16 +1092,16 @@
       <c r="O2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="P2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="14" t="s">
         <v>16</v>
       </c>
       <c r="R2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="S2" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1146,15 +1116,15 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="27"/>
+      <c r="K3" s="20"/>
       <c r="L3" s="8"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="11"/>
-      <c r="P3" s="27"/>
+      <c r="P3" s="20"/>
       <c r="Q3" s="12"/>
       <c r="R3" s="11"/>
-      <c r="S3" s="27"/>
+      <c r="S3" s="20"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
@@ -1167,15 +1137,15 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="28"/>
+      <c r="K4" s="21"/>
       <c r="L4" s="4"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="3"/>
-      <c r="P4" s="28"/>
+      <c r="P4" s="21"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="28"/>
+      <c r="S4" s="21"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
@@ -1188,15 +1158,15 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="28"/>
+      <c r="K5" s="21"/>
       <c r="L5" s="4"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="28"/>
+      <c r="P5" s="21"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="28"/>
+      <c r="S5" s="21"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
@@ -1209,15 +1179,15 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="28"/>
+      <c r="K6" s="21"/>
       <c r="L6" s="4"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="28"/>
+      <c r="P6" s="21"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="3"/>
-      <c r="S6" s="28"/>
+      <c r="S6" s="21"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
@@ -1230,15 +1200,15 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="28"/>
+      <c r="K7" s="21"/>
       <c r="L7" s="4"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="28"/>
+      <c r="P7" s="21"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="28"/>
+      <c r="S7" s="21"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
@@ -1251,15 +1221,15 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="28"/>
+      <c r="K8" s="21"/>
       <c r="L8" s="4"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="28"/>
+      <c r="P8" s="21"/>
       <c r="Q8" s="13"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="28"/>
+      <c r="S8" s="21"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
@@ -1272,15 +1242,15 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="28"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="28"/>
+      <c r="P9" s="21"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="28"/>
+      <c r="S9" s="21"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
@@ -1293,15 +1263,15 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="28"/>
+      <c r="K10" s="21"/>
       <c r="L10" s="4"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="3"/>
-      <c r="P10" s="28"/>
+      <c r="P10" s="21"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="28"/>
+      <c r="S10" s="21"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
@@ -1314,15 +1284,15 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="28"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="4"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="28"/>
+      <c r="P11" s="21"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="28"/>
+      <c r="S11" s="21"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
@@ -1335,15 +1305,15 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="28"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="4"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="28"/>
+      <c r="P12" s="21"/>
       <c r="Q12" s="13"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="28"/>
+      <c r="S12" s="21"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
@@ -1356,15 +1326,15 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="28"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="4"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="28"/>
+      <c r="P13" s="21"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="28"/>
+      <c r="S13" s="21"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
@@ -1377,15 +1347,15 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="21"/>
       <c r="L14" s="4"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="28"/>
+      <c r="P14" s="21"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="28"/>
+      <c r="S14" s="21"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="6"/>
@@ -1398,15 +1368,15 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="28"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="4"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="28"/>
+      <c r="P15" s="21"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="28"/>
+      <c r="S15" s="21"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
@@ -1419,15 +1389,15 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="28"/>
+      <c r="K16" s="21"/>
       <c r="L16" s="4"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="28"/>
+      <c r="P16" s="21"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="28"/>
+      <c r="S16" s="21"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
@@ -1440,15 +1410,15 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="28"/>
+      <c r="K17" s="21"/>
       <c r="L17" s="4"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="28"/>
+      <c r="P17" s="21"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="28"/>
+      <c r="S17" s="21"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
@@ -1461,15 +1431,15 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="28"/>
+      <c r="K18" s="21"/>
       <c r="L18" s="4"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="28"/>
+      <c r="P18" s="21"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="28"/>
+      <c r="S18" s="21"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
@@ -1482,15 +1452,15 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="28"/>
+      <c r="K19" s="21"/>
       <c r="L19" s="4"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="3"/>
-      <c r="P19" s="28"/>
+      <c r="P19" s="21"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="28"/>
+      <c r="S19" s="21"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
@@ -1503,15 +1473,15 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="28"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="4"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="3"/>
-      <c r="P20" s="28"/>
+      <c r="P20" s="21"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="28"/>
+      <c r="S20" s="21"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
@@ -1524,15 +1494,15 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="28"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="3"/>
-      <c r="P21" s="28"/>
+      <c r="P21" s="21"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="3"/>
-      <c r="S21" s="28"/>
+      <c r="S21" s="21"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
@@ -1545,15 +1515,15 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="28"/>
+      <c r="K22" s="21"/>
       <c r="L22" s="4"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="28"/>
+      <c r="P22" s="21"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="3"/>
-      <c r="S22" s="28"/>
+      <c r="S22" s="21"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
@@ -1566,15 +1536,15 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="28"/>
+      <c r="K23" s="21"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="28"/>
+      <c r="P23" s="21"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="3"/>
-      <c r="S23" s="28"/>
+      <c r="S23" s="21"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
@@ -1587,15 +1557,15 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="28"/>
+      <c r="K24" s="21"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="28"/>
+      <c r="P24" s="21"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="28"/>
+      <c r="S24" s="21"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="6"/>
@@ -1608,15 +1578,15 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="28"/>
+      <c r="K25" s="21"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="28"/>
+      <c r="P25" s="21"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="28"/>
+      <c r="S25" s="21"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
@@ -1629,15 +1599,15 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="28"/>
+      <c r="K26" s="21"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="28"/>
+      <c r="P26" s="21"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="28"/>
+      <c r="S26" s="21"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="6"/>
@@ -1650,15 +1620,15 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="28"/>
+      <c r="K27" s="21"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="3"/>
-      <c r="P27" s="28"/>
+      <c r="P27" s="21"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="28"/>
+      <c r="S27" s="21"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
@@ -1671,15 +1641,15 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="28"/>
+      <c r="K28" s="21"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="3"/>
-      <c r="P28" s="28"/>
+      <c r="P28" s="21"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="3"/>
-      <c r="S28" s="28"/>
+      <c r="S28" s="21"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="6"/>
@@ -1692,15 +1662,15 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="28"/>
+      <c r="K29" s="21"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="28"/>
+      <c r="P29" s="21"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="3"/>
-      <c r="S29" s="28"/>
+      <c r="S29" s="21"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
@@ -1713,15 +1683,15 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="28"/>
+      <c r="K30" s="21"/>
       <c r="L30" s="4"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="28"/>
+      <c r="P30" s="21"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="3"/>
-      <c r="S30" s="28"/>
+      <c r="S30" s="21"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="6"/>
@@ -1734,15 +1704,15 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="28"/>
+      <c r="K31" s="21"/>
       <c r="L31" s="4"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="3"/>
-      <c r="P31" s="28"/>
+      <c r="P31" s="21"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="28"/>
+      <c r="S31" s="21"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="6"/>
@@ -1755,15 +1725,15 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="28"/>
+      <c r="K32" s="21"/>
       <c r="L32" s="4"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="3"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="21"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="3"/>
-      <c r="S32" s="28"/>
+      <c r="S32" s="21"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="6"/>
@@ -1776,15 +1746,15 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="28"/>
+      <c r="K33" s="21"/>
       <c r="L33" s="4"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="28"/>
+      <c r="P33" s="21"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="28"/>
+      <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="6"/>
@@ -1797,15 +1767,15 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="28"/>
+      <c r="K34" s="21"/>
       <c r="L34" s="4"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="28"/>
+      <c r="P34" s="21"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="3"/>
-      <c r="S34" s="28"/>
+      <c r="S34" s="21"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="6"/>
@@ -1818,15 +1788,15 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="28"/>
+      <c r="K35" s="21"/>
       <c r="L35" s="4"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="3"/>
-      <c r="P35" s="28"/>
+      <c r="P35" s="21"/>
       <c r="Q35" s="13"/>
       <c r="R35" s="3"/>
-      <c r="S35" s="28"/>
+      <c r="S35" s="21"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="6"/>
@@ -1839,15 +1809,15 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="28"/>
+      <c r="K36" s="21"/>
       <c r="L36" s="4"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="3"/>
-      <c r="P36" s="28"/>
+      <c r="P36" s="21"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="3"/>
-      <c r="S36" s="28"/>
+      <c r="S36" s="21"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="6"/>
@@ -1860,15 +1830,15 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="28"/>
+      <c r="K37" s="21"/>
       <c r="L37" s="4"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="28"/>
+      <c r="P37" s="21"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="3"/>
-      <c r="S37" s="28"/>
+      <c r="S37" s="21"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="6"/>
@@ -1881,15 +1851,15 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="28"/>
+      <c r="K38" s="21"/>
       <c r="L38" s="4"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="28"/>
+      <c r="P38" s="21"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="3"/>
-      <c r="S38" s="28"/>
+      <c r="S38" s="21"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="6"/>
@@ -1902,15 +1872,15 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="28"/>
+      <c r="K39" s="21"/>
       <c r="L39" s="4"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="28"/>
+      <c r="P39" s="21"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="28"/>
+      <c r="S39" s="21"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="6"/>
@@ -1923,15 +1893,15 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="28"/>
+      <c r="K40" s="21"/>
       <c r="L40" s="4"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="28"/>
+      <c r="P40" s="21"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="28"/>
+      <c r="S40" s="21"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="6"/>
@@ -1944,15 +1914,15 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="28"/>
+      <c r="K41" s="21"/>
       <c r="L41" s="4"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="28"/>
+      <c r="P41" s="21"/>
       <c r="Q41" s="13"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="28"/>
+      <c r="S41" s="21"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="6"/>
@@ -1965,15 +1935,15 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="28"/>
+      <c r="K42" s="21"/>
       <c r="L42" s="4"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="28"/>
+      <c r="P42" s="21"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="3"/>
-      <c r="S42" s="28"/>
+      <c r="S42" s="21"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A43" s="6"/>
@@ -1986,15 +1956,15 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="28"/>
+      <c r="K43" s="21"/>
       <c r="L43" s="4"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="28"/>
+      <c r="P43" s="21"/>
       <c r="Q43" s="13"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="28"/>
+      <c r="S43" s="21"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="6"/>
@@ -2007,15 +1977,15 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="28"/>
+      <c r="K44" s="21"/>
       <c r="L44" s="4"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="28"/>
+      <c r="P44" s="21"/>
       <c r="Q44" s="13"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="28"/>
+      <c r="S44" s="21"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="6"/>
@@ -2028,15 +1998,15 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="28"/>
+      <c r="K45" s="21"/>
       <c r="L45" s="4"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="3"/>
-      <c r="P45" s="28"/>
+      <c r="P45" s="21"/>
       <c r="Q45" s="13"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="28"/>
+      <c r="S45" s="21"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="6"/>
@@ -2049,15 +2019,15 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="28"/>
+      <c r="K46" s="21"/>
       <c r="L46" s="4"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="3"/>
-      <c r="P46" s="28"/>
+      <c r="P46" s="21"/>
       <c r="Q46" s="13"/>
       <c r="R46" s="3"/>
-      <c r="S46" s="28"/>
+      <c r="S46" s="21"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="6"/>
@@ -2070,15 +2040,15 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="28"/>
+      <c r="K47" s="21"/>
       <c r="L47" s="4"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="3"/>
-      <c r="P47" s="28"/>
+      <c r="P47" s="21"/>
       <c r="Q47" s="13"/>
       <c r="R47" s="3"/>
-      <c r="S47" s="28"/>
+      <c r="S47" s="21"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="6"/>
@@ -2091,15 +2061,15 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="28"/>
+      <c r="K48" s="21"/>
       <c r="L48" s="4"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="3"/>
-      <c r="P48" s="28"/>
+      <c r="P48" s="21"/>
       <c r="Q48" s="13"/>
       <c r="R48" s="3"/>
-      <c r="S48" s="28"/>
+      <c r="S48" s="21"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="6"/>
@@ -2112,15 +2082,15 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="28"/>
+      <c r="K49" s="21"/>
       <c r="L49" s="4"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="28"/>
+      <c r="P49" s="21"/>
       <c r="Q49" s="13"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="28"/>
+      <c r="S49" s="21"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="6"/>
@@ -2133,15 +2103,15 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="28"/>
+      <c r="K50" s="21"/>
       <c r="L50" s="4"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="28"/>
+      <c r="P50" s="21"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="3"/>
-      <c r="S50" s="28"/>
+      <c r="S50" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/template/合宿前資料_テンプレ.xlsx
+++ b/template/合宿前資料_テンプレ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0bca17f66a05bfa2/ドキュメント/GitHub/huac_flight/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7A953E-942D-4A9F-8882-C28625805A67}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{ACC5DE24-4524-4578-95BE-99F0D08F9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F15168A-2C90-4663-913B-E429878955AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E53FFB89-D0E3-4E50-B074-2A2E6F2194C7}"/>
   </bookViews>
@@ -685,6 +685,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2122,6 +2126,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>